--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2317,6 +2317,822 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122238237</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98149</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norr Fågelsången, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>594902</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6654622</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sala socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122238239</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97109</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norr Fågelsången, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>594921</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6654635</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sala socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122238236</v>
+      </c>
+      <c r="B17" t="n">
+        <v>74733</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>308</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norr Fågelsången, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>594905</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6654578</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sala socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122238242</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91473</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1105</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Laxporing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Rhodonia placenta</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norr Fågelsången, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>594905</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6654861</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sala socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122238211</v>
+      </c>
+      <c r="B19" t="n">
+        <v>95687</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>54</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skogstrappmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Anastrophyllum michauxii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(F.Weber.) H.Buch</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norr Fågelsången, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>594901</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6654576</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sala socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122238232</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98149</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norr Fågelsången, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>594850</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6654472</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sala socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122238235</v>
+      </c>
+      <c r="B21" t="n">
+        <v>74725</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norr Fågelsången, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>594905</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6654578</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sala socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122238233</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98149</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norr Fågelsången, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>594875</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6654490</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sala socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122238237</v>
+        <v>122238242</v>
       </c>
       <c r="B15" t="n">
-        <v>98149</v>
+        <v>91480</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594902</v>
+        <v>594905</v>
       </c>
       <c r="R15" t="n">
-        <v>6654622</v>
+        <v>6654861</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238239</v>
+        <v>122238236</v>
       </c>
       <c r="B16" t="n">
-        <v>97109</v>
+        <v>74737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,25 +2433,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594921</v>
+        <v>594905</v>
       </c>
       <c r="R16" t="n">
-        <v>6654635</v>
+        <v>6654578</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122238236</v>
+        <v>122238232</v>
       </c>
       <c r="B17" t="n">
-        <v>74733</v>
+        <v>98157</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2535,25 +2535,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594905</v>
+        <v>594850</v>
       </c>
       <c r="R17" t="n">
-        <v>6654578</v>
+        <v>6654472</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122238242</v>
+        <v>122238239</v>
       </c>
       <c r="B18" t="n">
-        <v>91473</v>
+        <v>97117</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2637,25 +2637,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1105</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594905</v>
+        <v>594921</v>
       </c>
       <c r="R18" t="n">
-        <v>6654861</v>
+        <v>6654635</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238211</v>
+        <v>122238235</v>
       </c>
       <c r="B19" t="n">
-        <v>95687</v>
+        <v>74729</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,25 +2739,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>6439</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594901</v>
+        <v>594905</v>
       </c>
       <c r="R19" t="n">
-        <v>6654576</v>
+        <v>6654578</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122238232</v>
+        <v>122238237</v>
       </c>
       <c r="B20" t="n">
-        <v>98149</v>
+        <v>98157</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594850</v>
+        <v>594902</v>
       </c>
       <c r="R20" t="n">
-        <v>6654472</v>
+        <v>6654622</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122238235</v>
+        <v>122238211</v>
       </c>
       <c r="B21" t="n">
-        <v>74725</v>
+        <v>95695</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2943,25 +2943,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6439</v>
+        <v>54</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594905</v>
+        <v>594901</v>
       </c>
       <c r="R21" t="n">
-        <v>6654578</v>
+        <v>6654576</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3036,7 +3036,7 @@
         <v>122238233</v>
       </c>
       <c r="B22" t="n">
-        <v>98149</v>
+        <v>98157</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122238242</v>
+        <v>122238211</v>
       </c>
       <c r="B15" t="n">
-        <v>91480</v>
+        <v>95697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1105</v>
+        <v>54</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594905</v>
+        <v>594901</v>
       </c>
       <c r="R15" t="n">
-        <v>6654861</v>
+        <v>6654576</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238236</v>
+        <v>122238232</v>
       </c>
       <c r="B16" t="n">
-        <v>74737</v>
+        <v>98159</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,25 +2433,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594905</v>
+        <v>594850</v>
       </c>
       <c r="R16" t="n">
-        <v>6654578</v>
+        <v>6654472</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122238232</v>
+        <v>122238236</v>
       </c>
       <c r="B17" t="n">
-        <v>98157</v>
+        <v>74739</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2535,25 +2535,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594850</v>
+        <v>594905</v>
       </c>
       <c r="R17" t="n">
-        <v>6654472</v>
+        <v>6654578</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2628,7 +2628,7 @@
         <v>122238239</v>
       </c>
       <c r="B18" t="n">
-        <v>97117</v>
+        <v>97119</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238235</v>
+        <v>122238233</v>
       </c>
       <c r="B19" t="n">
-        <v>74729</v>
+        <v>98159</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,25 +2739,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594905</v>
+        <v>594875</v>
       </c>
       <c r="R19" t="n">
-        <v>6654578</v>
+        <v>6654490</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122238237</v>
+        <v>122238235</v>
       </c>
       <c r="B20" t="n">
-        <v>98157</v>
+        <v>74731</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,25 +2841,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594902</v>
+        <v>594905</v>
       </c>
       <c r="R20" t="n">
-        <v>6654622</v>
+        <v>6654578</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122238211</v>
+        <v>122238242</v>
       </c>
       <c r="B21" t="n">
-        <v>95695</v>
+        <v>91482</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2943,25 +2943,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>54</v>
+        <v>1105</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594901</v>
+        <v>594905</v>
       </c>
       <c r="R21" t="n">
-        <v>6654576</v>
+        <v>6654861</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122238233</v>
+        <v>122238237</v>
       </c>
       <c r="B22" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594875</v>
+        <v>594902</v>
       </c>
       <c r="R22" t="n">
-        <v>6654490</v>
+        <v>6654622</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122238211</v>
+        <v>122238233</v>
       </c>
       <c r="B15" t="n">
-        <v>95697</v>
+        <v>98159</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>54</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594901</v>
+        <v>594875</v>
       </c>
       <c r="R15" t="n">
-        <v>6654576</v>
+        <v>6654490</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238232</v>
+        <v>122238236</v>
       </c>
       <c r="B16" t="n">
-        <v>98159</v>
+        <v>74739</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,25 +2433,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594850</v>
+        <v>594905</v>
       </c>
       <c r="R16" t="n">
-        <v>6654472</v>
+        <v>6654578</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122238236</v>
+        <v>122238211</v>
       </c>
       <c r="B17" t="n">
-        <v>74739</v>
+        <v>95697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>54</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594905</v>
+        <v>594901</v>
       </c>
       <c r="R17" t="n">
-        <v>6654578</v>
+        <v>6654576</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122238239</v>
+        <v>122238237</v>
       </c>
       <c r="B18" t="n">
-        <v>97119</v>
+        <v>98159</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2637,25 +2637,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594921</v>
+        <v>594902</v>
       </c>
       <c r="R18" t="n">
-        <v>6654635</v>
+        <v>6654622</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238233</v>
+        <v>122238242</v>
       </c>
       <c r="B19" t="n">
-        <v>98159</v>
+        <v>91482</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2743,21 +2743,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594875</v>
+        <v>594905</v>
       </c>
       <c r="R19" t="n">
-        <v>6654490</v>
+        <v>6654861</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122238235</v>
+        <v>122238239</v>
       </c>
       <c r="B20" t="n">
-        <v>74731</v>
+        <v>97119</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2845,21 +2845,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6439</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594905</v>
+        <v>594921</v>
       </c>
       <c r="R20" t="n">
-        <v>6654578</v>
+        <v>6654635</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122238242</v>
+        <v>122238232</v>
       </c>
       <c r="B21" t="n">
-        <v>91482</v>
+        <v>98159</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594905</v>
+        <v>594850</v>
       </c>
       <c r="R21" t="n">
-        <v>6654861</v>
+        <v>6654472</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122238237</v>
+        <v>122238235</v>
       </c>
       <c r="B22" t="n">
-        <v>98159</v>
+        <v>74731</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3045,25 +3045,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594902</v>
+        <v>594905</v>
       </c>
       <c r="R22" t="n">
-        <v>6654622</v>
+        <v>6654578</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122238233</v>
+        <v>122238236</v>
       </c>
       <c r="B15" t="n">
-        <v>98159</v>
+        <v>74739</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594875</v>
+        <v>594905</v>
       </c>
       <c r="R15" t="n">
-        <v>6654490</v>
+        <v>6654578</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238236</v>
+        <v>122238232</v>
       </c>
       <c r="B16" t="n">
-        <v>74739</v>
+        <v>98175</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,25 +2433,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594905</v>
+        <v>594850</v>
       </c>
       <c r="R16" t="n">
-        <v>6654578</v>
+        <v>6654472</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122238211</v>
+        <v>122238239</v>
       </c>
       <c r="B17" t="n">
-        <v>95697</v>
+        <v>97135</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2535,25 +2535,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>54</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594901</v>
+        <v>594921</v>
       </c>
       <c r="R17" t="n">
-        <v>6654576</v>
+        <v>6654635</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122238237</v>
+        <v>122238242</v>
       </c>
       <c r="B18" t="n">
-        <v>98159</v>
+        <v>91498</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594902</v>
+        <v>594905</v>
       </c>
       <c r="R18" t="n">
-        <v>6654622</v>
+        <v>6654861</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238242</v>
+        <v>122238233</v>
       </c>
       <c r="B19" t="n">
-        <v>91482</v>
+        <v>98175</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2743,21 +2743,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594905</v>
+        <v>594875</v>
       </c>
       <c r="R19" t="n">
-        <v>6654861</v>
+        <v>6654490</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122238239</v>
+        <v>122238237</v>
       </c>
       <c r="B20" t="n">
-        <v>97119</v>
+        <v>98175</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,25 +2841,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594921</v>
+        <v>594902</v>
       </c>
       <c r="R20" t="n">
-        <v>6654635</v>
+        <v>6654622</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122238232</v>
+        <v>122238211</v>
       </c>
       <c r="B21" t="n">
-        <v>98159</v>
+        <v>95713</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2943,25 +2943,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>54</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594850</v>
+        <v>594901</v>
       </c>
       <c r="R21" t="n">
-        <v>6654472</v>
+        <v>6654576</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122238236</v>
+        <v>122238237</v>
       </c>
       <c r="B15" t="n">
-        <v>74739</v>
+        <v>98175</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594905</v>
+        <v>594902</v>
       </c>
       <c r="R15" t="n">
-        <v>6654578</v>
+        <v>6654622</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238232</v>
+        <v>122238235</v>
       </c>
       <c r="B16" t="n">
-        <v>98175</v>
+        <v>74731</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,25 +2433,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594850</v>
+        <v>594905</v>
       </c>
       <c r="R16" t="n">
-        <v>6654472</v>
+        <v>6654578</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122238242</v>
+        <v>122238211</v>
       </c>
       <c r="B18" t="n">
-        <v>91498</v>
+        <v>95713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2637,25 +2637,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1105</v>
+        <v>54</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594905</v>
+        <v>594901</v>
       </c>
       <c r="R18" t="n">
-        <v>6654861</v>
+        <v>6654576</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238233</v>
+        <v>122238242</v>
       </c>
       <c r="B19" t="n">
-        <v>98175</v>
+        <v>91498</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2743,21 +2743,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594875</v>
+        <v>594905</v>
       </c>
       <c r="R19" t="n">
-        <v>6654490</v>
+        <v>6654861</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122238237</v>
+        <v>122238236</v>
       </c>
       <c r="B20" t="n">
-        <v>98175</v>
+        <v>74739</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,25 +2841,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594902</v>
+        <v>594905</v>
       </c>
       <c r="R20" t="n">
-        <v>6654622</v>
+        <v>6654578</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122238211</v>
+        <v>122238232</v>
       </c>
       <c r="B21" t="n">
-        <v>95713</v>
+        <v>98175</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2943,25 +2943,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>54</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594901</v>
+        <v>594850</v>
       </c>
       <c r="R21" t="n">
-        <v>6654576</v>
+        <v>6654472</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122238235</v>
+        <v>122238233</v>
       </c>
       <c r="B22" t="n">
-        <v>74731</v>
+        <v>98175</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3045,25 +3045,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594905</v>
+        <v>594875</v>
       </c>
       <c r="R22" t="n">
-        <v>6654578</v>
+        <v>6654490</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122238237</v>
+        <v>122238211</v>
       </c>
       <c r="B15" t="n">
-        <v>98175</v>
+        <v>95723</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>54</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594902</v>
+        <v>594901</v>
       </c>
       <c r="R15" t="n">
-        <v>6654622</v>
+        <v>6654576</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238235</v>
+        <v>122238237</v>
       </c>
       <c r="B16" t="n">
-        <v>74731</v>
+        <v>98185</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,25 +2433,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594905</v>
+        <v>594902</v>
       </c>
       <c r="R16" t="n">
-        <v>6654578</v>
+        <v>6654622</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2526,7 +2526,7 @@
         <v>122238239</v>
       </c>
       <c r="B17" t="n">
-        <v>97135</v>
+        <v>97145</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122238211</v>
+        <v>122238236</v>
       </c>
       <c r="B18" t="n">
-        <v>95713</v>
+        <v>74739</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>54</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594901</v>
+        <v>594905</v>
       </c>
       <c r="R18" t="n">
-        <v>6654576</v>
+        <v>6654578</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238242</v>
+        <v>122238233</v>
       </c>
       <c r="B19" t="n">
-        <v>91498</v>
+        <v>98185</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2743,21 +2743,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594905</v>
+        <v>594875</v>
       </c>
       <c r="R19" t="n">
-        <v>6654861</v>
+        <v>6654490</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122238236</v>
+        <v>122238242</v>
       </c>
       <c r="B20" t="n">
-        <v>74739</v>
+        <v>91508</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,25 +2841,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>1105</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2872,7 +2872,7 @@
         <v>594905</v>
       </c>
       <c r="R20" t="n">
-        <v>6654578</v>
+        <v>6654861</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2934,7 +2934,7 @@
         <v>122238232</v>
       </c>
       <c r="B21" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122238233</v>
+        <v>122238235</v>
       </c>
       <c r="B22" t="n">
-        <v>98175</v>
+        <v>74731</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3045,25 +3045,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594875</v>
+        <v>594905</v>
       </c>
       <c r="R22" t="n">
-        <v>6654490</v>
+        <v>6654578</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122238211</v>
+        <v>122238232</v>
       </c>
       <c r="B15" t="n">
-        <v>95723</v>
+        <v>98185</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>54</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594901</v>
+        <v>594850</v>
       </c>
       <c r="R15" t="n">
-        <v>6654576</v>
+        <v>6654472</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238237</v>
+        <v>122238236</v>
       </c>
       <c r="B16" t="n">
-        <v>98185</v>
+        <v>74739</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,25 +2433,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594902</v>
+        <v>594905</v>
       </c>
       <c r="R16" t="n">
-        <v>6654622</v>
+        <v>6654578</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122238239</v>
+        <v>122238233</v>
       </c>
       <c r="B17" t="n">
-        <v>97145</v>
+        <v>98185</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2535,25 +2535,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594921</v>
+        <v>594875</v>
       </c>
       <c r="R17" t="n">
-        <v>6654635</v>
+        <v>6654490</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122238236</v>
+        <v>122238239</v>
       </c>
       <c r="B18" t="n">
-        <v>74739</v>
+        <v>97145</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2637,25 +2637,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594905</v>
+        <v>594921</v>
       </c>
       <c r="R18" t="n">
-        <v>6654578</v>
+        <v>6654635</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238233</v>
+        <v>122238211</v>
       </c>
       <c r="B19" t="n">
-        <v>98185</v>
+        <v>95723</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,25 +2739,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>54</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594875</v>
+        <v>594901</v>
       </c>
       <c r="R19" t="n">
-        <v>6654490</v>
+        <v>6654576</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122238242</v>
+        <v>122238235</v>
       </c>
       <c r="B20" t="n">
-        <v>91508</v>
+        <v>74731</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,25 +2841,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1105</v>
+        <v>6439</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2872,7 +2872,7 @@
         <v>594905</v>
       </c>
       <c r="R20" t="n">
-        <v>6654861</v>
+        <v>6654578</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2931,7 +2931,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122238232</v>
+        <v>122238237</v>
       </c>
       <c r="B21" t="n">
         <v>98185</v>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594850</v>
+        <v>594902</v>
       </c>
       <c r="R21" t="n">
-        <v>6654472</v>
+        <v>6654622</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122238235</v>
+        <v>122238242</v>
       </c>
       <c r="B22" t="n">
-        <v>74731</v>
+        <v>91508</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3045,25 +3045,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6439</v>
+        <v>1105</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3076,7 +3076,7 @@
         <v>594905</v>
       </c>
       <c r="R22" t="n">
-        <v>6654578</v>
+        <v>6654861</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122238232</v>
+        <v>122238236</v>
       </c>
       <c r="B15" t="n">
-        <v>98185</v>
+        <v>74744</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594850</v>
+        <v>594905</v>
       </c>
       <c r="R15" t="n">
-        <v>6654472</v>
+        <v>6654578</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238236</v>
+        <v>122238235</v>
       </c>
       <c r="B16" t="n">
-        <v>74739</v>
+        <v>74736</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,25 +2433,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122238233</v>
+        <v>122238239</v>
       </c>
       <c r="B17" t="n">
-        <v>98185</v>
+        <v>97157</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2535,25 +2535,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594875</v>
+        <v>594921</v>
       </c>
       <c r="R17" t="n">
-        <v>6654490</v>
+        <v>6654635</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122238239</v>
+        <v>122238232</v>
       </c>
       <c r="B18" t="n">
-        <v>97145</v>
+        <v>98197</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2637,25 +2637,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594921</v>
+        <v>594850</v>
       </c>
       <c r="R18" t="n">
-        <v>6654635</v>
+        <v>6654472</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238211</v>
+        <v>122238233</v>
       </c>
       <c r="B19" t="n">
-        <v>95723</v>
+        <v>98197</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,25 +2739,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594901</v>
+        <v>594875</v>
       </c>
       <c r="R19" t="n">
-        <v>6654576</v>
+        <v>6654490</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122238235</v>
+        <v>122238211</v>
       </c>
       <c r="B20" t="n">
-        <v>74731</v>
+        <v>95735</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,25 +2841,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6439</v>
+        <v>54</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594905</v>
+        <v>594901</v>
       </c>
       <c r="R20" t="n">
-        <v>6654578</v>
+        <v>6654576</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122238237</v>
+        <v>122238242</v>
       </c>
       <c r="B21" t="n">
-        <v>98185</v>
+        <v>91520</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594902</v>
+        <v>594905</v>
       </c>
       <c r="R21" t="n">
-        <v>6654622</v>
+        <v>6654861</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122238242</v>
+        <v>122238237</v>
       </c>
       <c r="B22" t="n">
-        <v>91508</v>
+        <v>98197</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594905</v>
+        <v>594902</v>
       </c>
       <c r="R22" t="n">
-        <v>6654861</v>
+        <v>6654622</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122238236</v>
+        <v>122238233</v>
       </c>
       <c r="B15" t="n">
-        <v>74744</v>
+        <v>98202</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594905</v>
+        <v>594875</v>
       </c>
       <c r="R15" t="n">
-        <v>6654578</v>
+        <v>6654490</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238235</v>
+        <v>122238236</v>
       </c>
       <c r="B16" t="n">
-        <v>74736</v>
+        <v>74744</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,25 +2433,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122238239</v>
+        <v>122238235</v>
       </c>
       <c r="B17" t="n">
-        <v>97157</v>
+        <v>74736</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>6439</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594921</v>
+        <v>594905</v>
       </c>
       <c r="R17" t="n">
-        <v>6654635</v>
+        <v>6654578</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122238232</v>
+        <v>122238237</v>
       </c>
       <c r="B18" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594850</v>
+        <v>594902</v>
       </c>
       <c r="R18" t="n">
-        <v>6654472</v>
+        <v>6654622</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238233</v>
+        <v>122238239</v>
       </c>
       <c r="B19" t="n">
-        <v>98197</v>
+        <v>97162</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,25 +2739,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594875</v>
+        <v>594921</v>
       </c>
       <c r="R19" t="n">
-        <v>6654490</v>
+        <v>6654635</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2832,7 +2832,7 @@
         <v>122238211</v>
       </c>
       <c r="B20" t="n">
-        <v>95735</v>
+        <v>95740</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>122238242</v>
       </c>
       <c r="B21" t="n">
-        <v>91520</v>
+        <v>91525</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122238237</v>
+        <v>122238232</v>
       </c>
       <c r="B22" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594902</v>
+        <v>594850</v>
       </c>
       <c r="R22" t="n">
-        <v>6654622</v>
+        <v>6654472</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122238233</v>
+        <v>122238236</v>
       </c>
       <c r="B15" t="n">
-        <v>98202</v>
+        <v>74745</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2331,25 +2331,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>308</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2359,10 +2354,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594875</v>
+        <v>594905</v>
       </c>
       <c r="R15" t="n">
-        <v>6654490</v>
+        <v>6654578</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2421,10 +2416,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238236</v>
+        <v>122238211</v>
       </c>
       <c r="B16" t="n">
-        <v>74744</v>
+        <v>95749</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2437,21 +2432,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Brunpudrad nållav</t>
-        </is>
+        <v>54</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2461,10 +2451,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594905</v>
+        <v>594901</v>
       </c>
       <c r="R16" t="n">
-        <v>6654578</v>
+        <v>6654576</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2523,10 +2513,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122238235</v>
+        <v>122238237</v>
       </c>
       <c r="B17" t="n">
-        <v>74736</v>
+        <v>98211</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2535,25 +2525,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6439</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Gulnål</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,10 +2548,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594905</v>
+        <v>594902</v>
       </c>
       <c r="R17" t="n">
-        <v>6654578</v>
+        <v>6654622</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2625,10 +2610,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122238237</v>
+        <v>122238232</v>
       </c>
       <c r="B18" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2643,11 +2628,6 @@
       <c r="E18" t="n">
         <v>220787</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2665,10 +2645,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594902</v>
+        <v>594850</v>
       </c>
       <c r="R18" t="n">
-        <v>6654622</v>
+        <v>6654472</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2727,10 +2707,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238239</v>
+        <v>122238233</v>
       </c>
       <c r="B19" t="n">
-        <v>97162</v>
+        <v>98211</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,25 +2719,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2767,10 +2742,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594921</v>
+        <v>594875</v>
       </c>
       <c r="R19" t="n">
-        <v>6654635</v>
+        <v>6654490</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2829,10 +2804,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122238211</v>
+        <v>122238239</v>
       </c>
       <c r="B20" t="n">
-        <v>95740</v>
+        <v>97171</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,25 +2816,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>54</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Skogstrappmossa</t>
-        </is>
+        <v>221941</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2869,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594901</v>
+        <v>594921</v>
       </c>
       <c r="R20" t="n">
-        <v>6654576</v>
+        <v>6654635</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2931,10 +2901,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122238242</v>
+        <v>122238235</v>
       </c>
       <c r="B21" t="n">
-        <v>91525</v>
+        <v>74737</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2943,25 +2913,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1105</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Laxporing</t>
-        </is>
+        <v>6439</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2974,7 +2939,7 @@
         <v>594905</v>
       </c>
       <c r="R21" t="n">
-        <v>6654861</v>
+        <v>6654578</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3033,10 +2998,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122238232</v>
+        <v>122238242</v>
       </c>
       <c r="B22" t="n">
-        <v>98202</v>
+        <v>91530</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3049,21 +3014,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>1105</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3073,10 +3033,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594850</v>
+        <v>594905</v>
       </c>
       <c r="R22" t="n">
-        <v>6654472</v>
+        <v>6654861</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122238236</v>
+        <v>122238211</v>
       </c>
       <c r="B15" t="n">
-        <v>74745</v>
+        <v>95762</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2335,16 +2335,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>54</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogstrappmossa</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2354,10 +2359,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594905</v>
+        <v>594901</v>
       </c>
       <c r="R15" t="n">
-        <v>6654578</v>
+        <v>6654576</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2416,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238211</v>
+        <v>122238237</v>
       </c>
       <c r="B16" t="n">
-        <v>95749</v>
+        <v>98224</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2428,20 +2433,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>54</v>
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2451,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594901</v>
+        <v>594902</v>
       </c>
       <c r="R16" t="n">
-        <v>6654576</v>
+        <v>6654622</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2513,10 +2523,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122238237</v>
+        <v>122238239</v>
       </c>
       <c r="B17" t="n">
-        <v>98211</v>
+        <v>97184</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2525,20 +2535,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221941</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2548,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594902</v>
+        <v>594921</v>
       </c>
       <c r="R17" t="n">
-        <v>6654622</v>
+        <v>6654635</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2610,10 +2625,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122238232</v>
+        <v>122238233</v>
       </c>
       <c r="B18" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2628,6 +2643,11 @@
       <c r="E18" t="n">
         <v>220787</v>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2645,10 +2665,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594850</v>
+        <v>594875</v>
       </c>
       <c r="R18" t="n">
-        <v>6654472</v>
+        <v>6654490</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2707,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238233</v>
+        <v>122238232</v>
       </c>
       <c r="B19" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2725,6 +2745,11 @@
       <c r="E19" t="n">
         <v>220787</v>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2742,10 +2767,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594875</v>
+        <v>594850</v>
       </c>
       <c r="R19" t="n">
-        <v>6654490</v>
+        <v>6654472</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2804,10 +2829,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122238239</v>
+        <v>122238235</v>
       </c>
       <c r="B20" t="n">
-        <v>97171</v>
+        <v>74741</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2820,16 +2845,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>6439</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2839,10 +2869,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594921</v>
+        <v>594905</v>
       </c>
       <c r="R20" t="n">
-        <v>6654635</v>
+        <v>6654578</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2901,10 +2931,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122238235</v>
+        <v>122238236</v>
       </c>
       <c r="B21" t="n">
-        <v>74737</v>
+        <v>74749</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2913,20 +2943,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6439</v>
+        <v>308</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3001,7 +3036,7 @@
         <v>122238242</v>
       </c>
       <c r="B22" t="n">
-        <v>91530</v>
+        <v>91543</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3015,6 +3050,11 @@
       </c>
       <c r="E22" t="n">
         <v>1105</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Laxporing</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122238211</v>
+        <v>122238232</v>
       </c>
       <c r="B15" t="n">
-        <v>95762</v>
+        <v>98237</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>54</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594901</v>
+        <v>594850</v>
       </c>
       <c r="R15" t="n">
-        <v>6654576</v>
+        <v>6654472</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238237</v>
+        <v>122238211</v>
       </c>
       <c r="B16" t="n">
-        <v>98224</v>
+        <v>95775</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,25 +2433,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>54</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594902</v>
+        <v>594901</v>
       </c>
       <c r="R16" t="n">
-        <v>6654622</v>
+        <v>6654576</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122238239</v>
+        <v>122238242</v>
       </c>
       <c r="B17" t="n">
-        <v>97184</v>
+        <v>91556</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2535,25 +2535,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>1105</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594921</v>
+        <v>594905</v>
       </c>
       <c r="R17" t="n">
-        <v>6654635</v>
+        <v>6654861</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122238233</v>
+        <v>122238236</v>
       </c>
       <c r="B18" t="n">
-        <v>98224</v>
+        <v>74749</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2637,25 +2637,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594875</v>
+        <v>594905</v>
       </c>
       <c r="R18" t="n">
-        <v>6654490</v>
+        <v>6654578</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238232</v>
+        <v>122238239</v>
       </c>
       <c r="B19" t="n">
-        <v>98224</v>
+        <v>97197</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,25 +2739,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594850</v>
+        <v>594921</v>
       </c>
       <c r="R19" t="n">
-        <v>6654472</v>
+        <v>6654635</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122238235</v>
+        <v>122238233</v>
       </c>
       <c r="B20" t="n">
-        <v>74741</v>
+        <v>98237</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,25 +2841,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594905</v>
+        <v>594875</v>
       </c>
       <c r="R20" t="n">
-        <v>6654578</v>
+        <v>6654490</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122238236</v>
+        <v>122238235</v>
       </c>
       <c r="B21" t="n">
-        <v>74749</v>
+        <v>74741</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2943,25 +2943,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122238242</v>
+        <v>122238237</v>
       </c>
       <c r="B22" t="n">
-        <v>91543</v>
+        <v>98237</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594905</v>
+        <v>594902</v>
       </c>
       <c r="R22" t="n">
-        <v>6654861</v>
+        <v>6654622</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122238232</v>
+        <v>122238211</v>
       </c>
       <c r="B15" t="n">
-        <v>98237</v>
+        <v>95775</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>54</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594850</v>
+        <v>594901</v>
       </c>
       <c r="R15" t="n">
-        <v>6654472</v>
+        <v>6654576</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238211</v>
+        <v>122238236</v>
       </c>
       <c r="B16" t="n">
-        <v>95775</v>
+        <v>74749</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>54</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594901</v>
+        <v>594905</v>
       </c>
       <c r="R16" t="n">
-        <v>6654576</v>
+        <v>6654578</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122238242</v>
+        <v>122238233</v>
       </c>
       <c r="B17" t="n">
-        <v>91556</v>
+        <v>98237</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594905</v>
+        <v>594875</v>
       </c>
       <c r="R17" t="n">
-        <v>6654861</v>
+        <v>6654490</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122238236</v>
+        <v>122238235</v>
       </c>
       <c r="B18" t="n">
-        <v>74749</v>
+        <v>74741</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2637,25 +2637,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238239</v>
+        <v>122238237</v>
       </c>
       <c r="B19" t="n">
-        <v>97197</v>
+        <v>98237</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,25 +2739,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594921</v>
+        <v>594902</v>
       </c>
       <c r="R19" t="n">
-        <v>6654635</v>
+        <v>6654622</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2829,7 +2829,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122238233</v>
+        <v>122238232</v>
       </c>
       <c r="B20" t="n">
         <v>98237</v>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594875</v>
+        <v>594850</v>
       </c>
       <c r="R20" t="n">
-        <v>6654490</v>
+        <v>6654472</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122238235</v>
+        <v>122238239</v>
       </c>
       <c r="B21" t="n">
-        <v>74741</v>
+        <v>97197</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6439</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594905</v>
+        <v>594921</v>
       </c>
       <c r="R21" t="n">
-        <v>6654578</v>
+        <v>6654635</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122238237</v>
+        <v>122238242</v>
       </c>
       <c r="B22" t="n">
-        <v>98237</v>
+        <v>91556</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594902</v>
+        <v>594905</v>
       </c>
       <c r="R22" t="n">
-        <v>6654622</v>
+        <v>6654861</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2421,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238236</v>
+        <v>122238233</v>
       </c>
       <c r="B16" t="n">
-        <v>74749</v>
+        <v>98237</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,25 +2433,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594905</v>
+        <v>594875</v>
       </c>
       <c r="R16" t="n">
-        <v>6654578</v>
+        <v>6654490</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122238233</v>
+        <v>122238236</v>
       </c>
       <c r="B17" t="n">
-        <v>98237</v>
+        <v>74749</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2535,25 +2535,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594875</v>
+        <v>594905</v>
       </c>
       <c r="R17" t="n">
-        <v>6654490</v>
+        <v>6654578</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2322,7 +2322,7 @@
         <v>122238211</v>
       </c>
       <c r="B15" t="n">
-        <v>95775</v>
+        <v>95777</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238233</v>
+        <v>122238232</v>
       </c>
       <c r="B16" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594875</v>
+        <v>594850</v>
       </c>
       <c r="R16" t="n">
-        <v>6654490</v>
+        <v>6654472</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122238236</v>
+        <v>122238242</v>
       </c>
       <c r="B17" t="n">
-        <v>74749</v>
+        <v>91557</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2535,25 +2535,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>1105</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2566,7 +2566,7 @@
         <v>594905</v>
       </c>
       <c r="R17" t="n">
-        <v>6654578</v>
+        <v>6654861</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122238235</v>
+        <v>122238233</v>
       </c>
       <c r="B18" t="n">
-        <v>74741</v>
+        <v>98240</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2637,25 +2637,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594905</v>
+        <v>594875</v>
       </c>
       <c r="R18" t="n">
-        <v>6654578</v>
+        <v>6654490</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238237</v>
+        <v>122238239</v>
       </c>
       <c r="B19" t="n">
-        <v>98237</v>
+        <v>97200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,25 +2739,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594902</v>
+        <v>594921</v>
       </c>
       <c r="R19" t="n">
-        <v>6654622</v>
+        <v>6654635</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122238232</v>
+        <v>122238236</v>
       </c>
       <c r="B20" t="n">
-        <v>98237</v>
+        <v>74749</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,25 +2841,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594850</v>
+        <v>594905</v>
       </c>
       <c r="R20" t="n">
-        <v>6654472</v>
+        <v>6654578</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122238239</v>
+        <v>122238237</v>
       </c>
       <c r="B21" t="n">
-        <v>97197</v>
+        <v>98240</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2943,25 +2943,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594921</v>
+        <v>594902</v>
       </c>
       <c r="R21" t="n">
-        <v>6654635</v>
+        <v>6654622</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122238242</v>
+        <v>122238235</v>
       </c>
       <c r="B22" t="n">
-        <v>91556</v>
+        <v>74741</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3045,25 +3045,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1105</v>
+        <v>6439</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3076,7 +3076,7 @@
         <v>594905</v>
       </c>
       <c r="R22" t="n">
-        <v>6654861</v>
+        <v>6654578</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122238211</v>
+        <v>122238233</v>
       </c>
       <c r="B15" t="n">
-        <v>95777</v>
+        <v>98240</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>54</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594901</v>
+        <v>594875</v>
       </c>
       <c r="R15" t="n">
-        <v>6654576</v>
+        <v>6654490</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238232</v>
+        <v>122238242</v>
       </c>
       <c r="B16" t="n">
-        <v>98240</v>
+        <v>91557</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594850</v>
+        <v>594905</v>
       </c>
       <c r="R16" t="n">
-        <v>6654472</v>
+        <v>6654861</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122238242</v>
+        <v>122238232</v>
       </c>
       <c r="B17" t="n">
-        <v>91557</v>
+        <v>98240</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594905</v>
+        <v>594850</v>
       </c>
       <c r="R17" t="n">
-        <v>6654861</v>
+        <v>6654472</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2625,7 +2625,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122238233</v>
+        <v>122238237</v>
       </c>
       <c r="B18" t="n">
         <v>98240</v>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594875</v>
+        <v>594902</v>
       </c>
       <c r="R18" t="n">
-        <v>6654490</v>
+        <v>6654622</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238239</v>
+        <v>122238235</v>
       </c>
       <c r="B19" t="n">
-        <v>97200</v>
+        <v>74741</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2743,21 +2743,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>6439</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594921</v>
+        <v>594905</v>
       </c>
       <c r="R19" t="n">
-        <v>6654635</v>
+        <v>6654578</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122238236</v>
+        <v>122238239</v>
       </c>
       <c r="B20" t="n">
-        <v>74749</v>
+        <v>97200</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,25 +2841,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594905</v>
+        <v>594921</v>
       </c>
       <c r="R20" t="n">
-        <v>6654578</v>
+        <v>6654635</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122238237</v>
+        <v>122238211</v>
       </c>
       <c r="B21" t="n">
-        <v>98240</v>
+        <v>95777</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2943,25 +2943,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>54</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594902</v>
+        <v>594901</v>
       </c>
       <c r="R21" t="n">
-        <v>6654622</v>
+        <v>6654576</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122238235</v>
+        <v>122238236</v>
       </c>
       <c r="B22" t="n">
-        <v>74741</v>
+        <v>74749</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3045,25 +3045,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91858388</v>
+        <v>98450503</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väst Nygruvskärret, Vstm</t>
+          <t>Väst Nygruvkärret, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594942.8313949662</v>
+        <v>594802</v>
       </c>
       <c r="R2" t="n">
-        <v>6654998.142326653</v>
+        <v>6654521</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,81 +754,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre barrskog, örtstråk</t>
+          <t>Äldre barrblandskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91858387</v>
+        <v>98450505</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väst Nygruvskärret, Vstm</t>
+          <t>Väst Nygruvkärret, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594914.9572672304</v>
+        <v>594858</v>
       </c>
       <c r="R3" t="n">
-        <v>6654893.898498127</v>
+        <v>6654549</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,78 +856,83 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrskog, örtstråk</t>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91858383</v>
+        <v>122238211</v>
       </c>
       <c r="B4" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>54</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väst Nygruvskärret, Vstm</t>
+          <t>Norr Fågelsången, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594921.8817426325</v>
+        <v>594901</v>
       </c>
       <c r="R4" t="n">
-        <v>6654624.995943074</v>
+        <v>6654576</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,22 +959,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,78 +973,63 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Äldre talldominerad barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91858386</v>
+        <v>122238236</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väst Nygruvskärret, Vstm</t>
+          <t>Norr Fågelsången, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594892.9349321385</v>
+        <v>594905</v>
       </c>
       <c r="R5" t="n">
-        <v>6654795.804433665</v>
+        <v>6654578</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1115,22 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,39 +1070,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91858390</v>
+        <v>122238242</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,38 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väst Nygruvskärret, Vstm</t>
+          <t>Norr Fågelsången, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594852.8193549262</v>
+        <v>594905</v>
       </c>
       <c r="R6" t="n">
-        <v>6654505.176627561</v>
+        <v>6654861</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1237,22 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,39 +1167,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Äldre barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98450507</v>
+        <v>122238231</v>
       </c>
       <c r="B7" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,37 +1196,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väst Nygruvkärret, Vstm</t>
+          <t>Norr Fågelsången, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594913.2954827785</v>
+        <v>594808</v>
       </c>
       <c r="R7" t="n">
-        <v>6654588.762548762</v>
+        <v>6654481</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,22 +1250,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,36 +1266,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98450504</v>
+        <v>122238240</v>
       </c>
       <c r="B8" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,46 +1293,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4368</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väst Nygruvkärret, Vstm</t>
+          <t>Norr Fågelsången, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594875.3804120419</v>
+        <v>594934</v>
       </c>
       <c r="R8" t="n">
-        <v>6654426.727261041</v>
+        <v>6654635</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1481,22 +1347,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,74 +1363,68 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98450505</v>
+        <v>91858376</v>
       </c>
       <c r="B9" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väst Nygruvkärret, Vstm</t>
+          <t>Väst Nygruvskärret, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594857.6958027559</v>
+        <v>594789</v>
       </c>
       <c r="R9" t="n">
-        <v>6654549.318046841</v>
+        <v>6654364</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1598,22 +1448,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,53 +1462,39 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>Liggande murken tallstam</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98450509</v>
+        <v>98450512</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,43 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Väst Nygruvkärret, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594914.4861428025</v>
+        <v>594917</v>
       </c>
       <c r="R10" t="n">
-        <v>6654639.810532908</v>
+        <v>6654972</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1742,21 +1559,11 @@
           <t>2021-10-28</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-10-28</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1769,21 +1576,6 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1801,50 +1593,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>98450508</v>
+        <v>98450504</v>
       </c>
       <c r="B11" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>4368</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Väst Nygruvkärret, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594925.6039935107</v>
+        <v>594875</v>
       </c>
       <c r="R11" t="n">
-        <v>6654636.095485789</v>
+        <v>6654426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,19 +1670,9 @@
           <t>2021-10-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1918,15 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>98450513</v>
+        <v>98450509</v>
       </c>
       <c r="B12" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,34 +1715,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Väst Nygruvkärret, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594965.3982698802</v>
+        <v>594915</v>
       </c>
       <c r="R12" t="n">
-        <v>6654997.223356658</v>
+        <v>6654640</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1991,21 +1781,11 @@
           <t>2021-10-28</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-10-28</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2018,6 +1798,21 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2035,69 +1830,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>98450510</v>
+        <v>122238234</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väst Nygruvkärret, Vstm</t>
+          <t>Norr Fågelsången, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594925.7700072981</v>
+        <v>594929</v>
       </c>
       <c r="R13" t="n">
-        <v>6654649.104080656</v>
+        <v>6654580</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2121,22 +1895,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2145,101 +1909,66 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>0 substratenheter</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>98450506</v>
+        <v>122238235</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väst Nygruvkärret, Vstm</t>
+          <t>Norr Fågelsången, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594849.3880783513</v>
+        <v>594905</v>
       </c>
       <c r="R14" t="n">
-        <v>6654580.115193333</v>
+        <v>6654578</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2263,22 +1992,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2287,85 +2006,66 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>0 substratenheter</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122238233</v>
+        <v>98450507</v>
       </c>
       <c r="B15" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norr Fågelsången, Vstm</t>
+          <t>Väst Nygruvkärret, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594875</v>
+        <v>594914</v>
       </c>
       <c r="R15" t="n">
-        <v>6654490</v>
+        <v>6654589</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2389,12 +2089,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2405,31 +2105,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122238242</v>
+        <v>91858389</v>
       </c>
       <c r="B16" t="n">
-        <v>91557</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2437,34 +2137,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norr Fågelsången, Vstm</t>
+          <t>Väst Nygruvskärret, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594905</v>
+        <v>594778</v>
       </c>
       <c r="R16" t="n">
-        <v>6654861</v>
+        <v>6654333</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2491,12 +2195,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2505,33 +2209,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Ädre barrskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122238232</v>
+        <v>91858390</v>
       </c>
       <c r="B17" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,16 +2262,20 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norr Fågelsången, Vstm</t>
+          <t>Väst Nygruvskärret, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594850</v>
+        <v>594853</v>
       </c>
       <c r="R17" t="n">
-        <v>6654472</v>
+        <v>6654505</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2593,12 +2302,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2607,33 +2316,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre barrskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122238237</v>
+        <v>98450506</v>
       </c>
       <c r="B18" t="n">
-        <v>98240</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2658,20 +2368,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norr Fågelsången, Vstm</t>
+          <t>Väst Nygruvkärret, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594902</v>
+        <v>594850</v>
       </c>
       <c r="R18" t="n">
-        <v>6654622</v>
+        <v>6654580</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2695,12 +2421,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2709,71 +2435,96 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>0 substratenheter</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122238235</v>
+        <v>98450510</v>
       </c>
       <c r="B19" t="n">
-        <v>74741</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norr Fågelsången, Vstm</t>
+          <t>Väst Nygruvkärret, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594905</v>
+        <v>594926</v>
       </c>
       <c r="R19" t="n">
-        <v>6654578</v>
+        <v>6654649</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2797,12 +2548,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2811,55 +2562,64 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>0 substratenheter</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122238239</v>
+        <v>122238232</v>
       </c>
       <c r="B20" t="n">
-        <v>97200</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2869,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594921</v>
+        <v>594850</v>
       </c>
       <c r="R20" t="n">
-        <v>6654635</v>
+        <v>6654472</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2931,37 +2691,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122238211</v>
+        <v>122238233</v>
       </c>
       <c r="B21" t="n">
-        <v>95777</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>54</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2971,10 +2726,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594901</v>
+        <v>594875</v>
       </c>
       <c r="R21" t="n">
-        <v>6654576</v>
+        <v>6654490</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3033,37 +2788,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122238236</v>
+        <v>122238237</v>
       </c>
       <c r="B22" t="n">
-        <v>74749</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3073,10 +2823,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594905</v>
+        <v>594902</v>
       </c>
       <c r="R22" t="n">
-        <v>6654578</v>
+        <v>6654622</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3132,6 +2882,735 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>91858383</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Väst Nygruvskärret, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>594922</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6654625</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sala socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Äldre talldominerad barrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>98450508</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Väst Nygruvkärret, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>594926</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6654636</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sala socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-10-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-10-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122238239</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norr Fågelsången, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>594921</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6654635</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sala socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>91858386</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Väst Nygruvskärret, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>594893</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6654796</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sala socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>91858387</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Väst Nygruvskärret, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>594915</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6654894</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sala socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Barrskog, örtstråk</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>91858388</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Väst Nygruvskärret, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>594943</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6654998</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sala socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Äldre barrskog, örtstråk</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>98450513</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Väst Nygruvkärret, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>594965</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6654997</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sala socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2021-10-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2021-10-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22353-2024 artfynd.xlsx
+++ b/artfynd/A 22353-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450503</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450505</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122238211</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122238236</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122238242</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122238231</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122238240</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91858376</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450512</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450504</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450509</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1924,6 +1984,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122238234</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2021,6 +2086,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122238235</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2123,6 +2193,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450507</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2230,6 +2305,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91858389</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2337,6 +2417,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91858390</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2464,6 +2549,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450506</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2591,6 +2681,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450510</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2688,6 +2783,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122238232</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2785,6 +2885,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122238233</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2882,6 +2987,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122238237</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2989,6 +3099,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91858383</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3091,6 +3206,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450508</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3188,6 +3308,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122238239</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3295,6 +3420,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91858386</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3402,6 +3532,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91858387</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3509,6 +3644,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91858388</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3611,8 +3751,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450513</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>